--- a/warehouse_gui_server/사용자1주문.xlsx
+++ b/warehouse_gui_server/사용자1주문.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C438"/>
+  <dimension ref="A1:C439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,11 +446,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>드롭스</t>
+          <t>롤리팝</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -459,11 +459,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>껌</t>
+          <t>버터스카치</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -476,33 +476,33 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>캔디 케인</t>
+          <t>퍼지</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>누룽지 사탕</t>
+          <t>드롭스</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -511,11 +511,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>껌</t>
+          <t>후르츠 캔디</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -537,11 +537,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>비타민 캔디</t>
+          <t>롤리팝</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -563,24 +563,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>롤리팝</t>
+          <t>비타민 캔디</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>박하사탕</t>
+          <t>껌</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -589,7 +589,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>계피사탕</t>
+          <t>박하사탕</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -602,20 +602,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>캔디 케인</t>
+          <t>계피사탕</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>목캔디</t>
+          <t>캔디 케인</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -628,11 +628,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>계피사탕</t>
+          <t>목캔디</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -641,20 +641,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>팝핑 캔디</t>
+          <t>계피사탕</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>캔디 케인</t>
+          <t>팝핑 캔디</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -667,7 +667,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>젤리빈</t>
+          <t>캔디 케인</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -680,7 +680,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>비타민 캔디</t>
+          <t>젤리빈</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -693,11 +693,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>후르츠 캔디</t>
+          <t>비타민 캔디</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -706,11 +706,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>드롭스</t>
+          <t>후르츠 캔디</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -719,7 +719,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>알사탕</t>
+          <t>드롭스</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -728,11 +728,11 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>퍼지</t>
+          <t>알사탕</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -745,7 +745,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>후르츠 캔디</t>
+          <t>퍼지</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -758,7 +758,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>누룽지 사탕</t>
+          <t>후르츠 캔디</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -771,7 +771,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>계피사탕</t>
+          <t>누룽지 사탕</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -784,11 +784,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>껌</t>
+          <t>계피사탕</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -797,24 +797,24 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>버터스카치</t>
+          <t>껌</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>누가</t>
+          <t>버터스카치</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -823,11 +823,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>버터스카치</t>
+          <t>누가</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -836,7 +836,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>토피</t>
+          <t>버터스카치</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -845,15 +845,15 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>무설탕 캔디</t>
+          <t>토피</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -862,11 +862,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>후르츠 캔디</t>
+          <t>무설탕 캔디</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -875,7 +875,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>롤리팝</t>
+          <t>후르츠 캔디</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -888,7 +888,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>껌</t>
+          <t>롤리팝</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>젤리빈</t>
+          <t>껌</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -910,15 +910,15 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>누가</t>
+          <t>젤리빈</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -927,11 +927,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>박하사탕</t>
+          <t>누가</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -940,7 +940,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>목캔디</t>
+          <t>박하사탕</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -949,15 +949,15 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>락 캔디</t>
+          <t>목캔디</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -966,7 +966,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>무설탕 캔디</t>
+          <t>락 캔디</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -979,7 +979,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>토피</t>
+          <t>무설탕 캔디</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -992,7 +992,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>비타민 캔디</t>
+          <t>토피</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1005,24 +1005,24 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>계피사탕</t>
+          <t>비타민 캔디</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>롤리팝</t>
+          <t>계피사탕</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -1031,11 +1031,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>코튼 캔디</t>
+          <t>롤리팝</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>캔디 케인</t>
+          <t>코튼 캔디</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1053,15 +1053,15 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>박하사탕</t>
+          <t>캔디 케인</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -1070,11 +1070,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>캔디 케인</t>
+          <t>박하사탕</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -1083,11 +1083,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>버터스카치</t>
+          <t>캔디 케인</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -1096,11 +1096,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>누가</t>
+          <t>버터스카치</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>후르츠 캔디</t>
+          <t>누가</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1118,11 +1118,11 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>락 캔디</t>
+          <t>후르츠 캔디</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>토피</t>
+          <t>락 캔디</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>알사탕</t>
+          <t>토피</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>팝핑 캔디</t>
+          <t>알사탕</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>껌</t>
+          <t>팝핑 캔디</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>계피사탕</t>
+          <t>껌</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1196,11 +1196,11 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>팝핑 캔디</t>
+          <t>계피사탕</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -1213,11 +1213,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>코튼 캔디</t>
+          <t>팝핑 캔디</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -1226,11 +1226,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>락 캔디</t>
+          <t>코튼 캔디</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -1239,11 +1239,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>박하사탕</t>
+          <t>락 캔디</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>무설탕 캔디</t>
+          <t>박하사탕</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -1261,11 +1261,11 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>목캔디</t>
+          <t>무설탕 캔디</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -1278,11 +1278,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>껌</t>
+          <t>목캔디</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>캔디 케인</t>
+          <t>껌</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>알사탕</t>
+          <t>캔디 케인</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -1313,11 +1313,11 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>누가</t>
+          <t>알사탕</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>후르츠 캔디</t>
+          <t>누가</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -1343,11 +1343,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>락 캔디</t>
+          <t>후르츠 캔디</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>목캔디</t>
+          <t>락 캔디</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -1369,11 +1369,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>캔디 케인</t>
+          <t>목캔디</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>퍼지</t>
+          <t>캔디 케인</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -1391,11 +1391,11 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>캔디 케인</t>
+          <t>퍼지</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -1408,11 +1408,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>롤리팝</t>
+          <t>캔디 케인</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -1421,20 +1421,20 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>퍼지</t>
+          <t>롤리팝</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>후르츠 캔디</t>
+          <t>퍼지</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -1447,11 +1447,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>박하사탕</t>
+          <t>후르츠 캔디</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>계피사탕</t>
+          <t>박하사탕</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>비타민 캔디</t>
+          <t>계피사탕</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -1486,11 +1486,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>퍼지</t>
+          <t>비타민 캔디</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -1499,24 +1499,24 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>코튼 캔디</t>
+          <t>퍼지</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>누가</t>
+          <t>코튼 캔디</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -1525,11 +1525,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>락 캔디</t>
+          <t>누가</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -1538,11 +1538,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>젤리빈</t>
+          <t>락 캔디</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>누룽지 사탕</t>
+          <t>젤리빈</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>후르츠 캔디</t>
+          <t>누룽지 사탕</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -1577,24 +1577,24 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>팝핑 캔디</t>
+          <t>후르츠 캔디</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>껌</t>
+          <t>팝핑 캔디</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -1603,11 +1603,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>목캔디</t>
+          <t>껌</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -1616,11 +1616,11 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>후르츠 캔디</t>
+          <t>목캔디</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -1629,16 +1629,16 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>비타민 캔디</t>
+          <t>후르츠 캔디</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>누가</t>
+          <t>비타민 캔디</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>토피</t>
+          <t>누가</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>캔디 케인</t>
+          <t>토피</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -1694,11 +1694,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>누룽지 사탕</t>
+          <t>캔디 케인</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -1707,20 +1707,20 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>구미</t>
+          <t>누룽지 사탕</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>박하사탕</t>
+          <t>구미</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>롤리팝</t>
+          <t>박하사탕</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -1746,11 +1746,11 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>버터스카치</t>
+          <t>롤리팝</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -1759,11 +1759,11 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>누룽지 사탕</t>
+          <t>버터스카치</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
@@ -1772,11 +1772,11 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>알사탕</t>
+          <t>누룽지 사탕</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -1785,20 +1785,20 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>태피</t>
+          <t>알사탕</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>누가</t>
+          <t>태피</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -1811,11 +1811,11 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>무설탕 캔디</t>
+          <t>누가</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -1824,20 +1824,20 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>젤리빈</t>
+          <t>무설탕 캔디</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>목캔디</t>
+          <t>젤리빈</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -1850,11 +1850,11 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>드롭스</t>
+          <t>목캔디</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -1863,11 +1863,11 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>코튼 캔디</t>
+          <t>드롭스</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
@@ -1876,11 +1876,11 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>껌</t>
+          <t>코튼 캔디</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>버터스카치</t>
+          <t>껌</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -1898,11 +1898,11 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>락 캔디</t>
+          <t>버터스카치</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>퍼지</t>
+          <t>락 캔디</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -1928,11 +1928,11 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>버터스카치</t>
+          <t>퍼지</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
@@ -1941,11 +1941,11 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>캐러멜</t>
+          <t>버터스카치</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>태피</t>
+          <t>캐러멜</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -1963,15 +1963,15 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>젤리빈</t>
+          <t>태피</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
@@ -1980,11 +1980,11 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>드롭스</t>
+          <t>젤리빈</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
@@ -1993,11 +1993,11 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>껌</t>
+          <t>드롭스</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>후르츠 캔디</t>
+          <t>껌</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -2015,11 +2015,11 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>구미</t>
+          <t>후르츠 캔디</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>버터스카치</t>
+          <t>구미</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>락 캔디</t>
+          <t>버터스카치</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -2058,24 +2058,24 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>캐러멜</t>
+          <t>락 캔디</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>누룽지 사탕</t>
+          <t>캐러멜</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>토피</t>
+          <t>누룽지 사탕</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>알사탕</t>
+          <t>토피</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>목캔디</t>
+          <t>알사탕</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -2119,11 +2119,11 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>무설탕 캔디</t>
+          <t>목캔디</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>퍼지</t>
+          <t>무설탕 캔디</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -2149,20 +2149,20 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>마시멜로</t>
+          <t>퍼지</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>버터스카치</t>
+          <t>마시멜로</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>토피</t>
+          <t>버터스카치</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -2188,24 +2188,24 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>캐러멜</t>
+          <t>토피</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>롤리팝</t>
+          <t>캐러멜</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
@@ -2214,11 +2214,11 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>캔디 케인</t>
+          <t>롤리팝</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140">
@@ -2227,11 +2227,11 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>비타민 캔디</t>
+          <t>캔디 케인</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
@@ -2240,24 +2240,24 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>박하사탕</t>
+          <t>비타민 캔디</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>껌</t>
+          <t>박하사탕</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>마시멜로</t>
+          <t>껌</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -2279,20 +2279,20 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>박하사탕</t>
+          <t>마시멜로</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>누룽지 사탕</t>
+          <t>박하사탕</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>코튼 캔디</t>
+          <t>누룽지 사탕</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>마시멜로</t>
+          <t>코튼 캔디</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>목캔디</t>
+          <t>마시멜로</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -2340,11 +2340,11 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>후르츠 캔디</t>
+          <t>목캔디</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>구미</t>
+          <t>후르츠 캔디</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>무설탕 캔디</t>
+          <t>구미</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>태피</t>
+          <t>무설탕 캔디</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -2392,11 +2392,11 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>목캔디</t>
+          <t>태피</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>껌</t>
+          <t>목캔디</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>팝핑 캔디</t>
+          <t>껌</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -2435,24 +2435,24 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>계피사탕</t>
+          <t>팝핑 캔디</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>누가</t>
+          <t>계피사탕</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>코튼 캔디</t>
+          <t>누가</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -2474,11 +2474,11 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>락 캔디</t>
+          <t>코튼 캔디</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160">
@@ -2487,11 +2487,11 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>토피</t>
+          <t>락 캔디</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161">
@@ -2500,20 +2500,20 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>젤리빈</t>
+          <t>토피</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>버터스카치</t>
+          <t>젤리빈</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -2526,11 +2526,11 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>캔디 케인</t>
+          <t>버터스카치</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>팝핑 캔디</t>
+          <t>캔디 케인</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -2552,11 +2552,11 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>박하사탕</t>
+          <t>팝핑 캔디</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166">
@@ -2565,11 +2565,11 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>퍼지</t>
+          <t>박하사탕</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="167">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>드롭스</t>
+          <t>퍼지</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -2587,15 +2587,15 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>비타민 캔디</t>
+          <t>드롭스</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169">
@@ -2604,11 +2604,11 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>캔디 케인</t>
+          <t>비타민 캔디</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="170">
@@ -2617,11 +2617,11 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>드롭스</t>
+          <t>캔디 케인</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171">
@@ -2630,20 +2630,20 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>박하사탕</t>
+          <t>드롭스</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>캔디 케인</t>
+          <t>박하사탕</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>박하사탕</t>
+          <t>캔디 케인</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>롤리팝</t>
+          <t>박하사탕</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -2678,15 +2678,15 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>박하사탕</t>
+          <t>롤리팝</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>구미</t>
+          <t>박하사탕</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -2708,11 +2708,11 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>캔디 케인</t>
+          <t>구미</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="178">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>후르츠 캔디</t>
+          <t>캔디 케인</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>코튼 캔디</t>
+          <t>후르츠 캔디</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -2743,11 +2743,11 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>계피사탕</t>
+          <t>코튼 캔디</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>목캔디</t>
+          <t>계피사탕</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -2773,11 +2773,11 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>누룽지 사탕</t>
+          <t>목캔디</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>비타민 캔디</t>
+          <t>누룽지 사탕</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -2799,11 +2799,11 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>락 캔디</t>
+          <t>비타민 캔디</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>마시멜로</t>
+          <t>락 캔디</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -2821,7 +2821,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187">
@@ -2838,11 +2838,11 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>태피</t>
+          <t>마시멜로</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>계피사탕</t>
+          <t>태피</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>버터스카치</t>
+          <t>계피사탕</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -2873,11 +2873,11 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>코튼 캔디</t>
+          <t>버터스카치</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>태피</t>
+          <t>코튼 캔디</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>토피</t>
+          <t>태피</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -2912,15 +2912,15 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>태피</t>
+          <t>토피</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194">
@@ -2929,11 +2929,11 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>젤리빈</t>
+          <t>태피</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="195">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>롤리팝</t>
+          <t>젤리빈</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>락 캔디</t>
+          <t>롤리팝</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>버터스카치</t>
+          <t>락 캔디</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>코튼 캔디</t>
+          <t>버터스카치</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -2990,15 +2990,15 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>껌</t>
+          <t>코튼 캔디</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200">
@@ -3007,11 +3007,11 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>퍼지</t>
+          <t>껌</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="201">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>버터스카치</t>
+          <t>퍼지</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>캔디 케인</t>
+          <t>버터스카치</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>계피사탕</t>
+          <t>캔디 케인</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>무설탕 캔디</t>
+          <t>계피사탕</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -3068,11 +3068,11 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>누룽지 사탕</t>
+          <t>무설탕 캔디</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -3085,11 +3085,11 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>태피</t>
+          <t>누룽지 사탕</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="207">
@@ -3098,11 +3098,11 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>알사탕</t>
+          <t>태피</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="208">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>후르츠 캔디</t>
+          <t>알사탕</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -3124,11 +3124,11 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>젤리빈</t>
+          <t>후르츠 캔디</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210">
@@ -3137,24 +3137,24 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>캔디 케인</t>
+          <t>젤리빈</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>젤리빈</t>
+          <t>캔디 케인</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="212">
@@ -3163,11 +3163,11 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>목캔디</t>
+          <t>젤리빈</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="213">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>버터스카치</t>
+          <t>목캔디</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -3185,11 +3185,11 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>락 캔디</t>
+          <t>버터스카치</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -3202,11 +3202,11 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>목캔디</t>
+          <t>락 캔디</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="216">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>드롭스</t>
+          <t>목캔디</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -3224,15 +3224,15 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>캔디 케인</t>
+          <t>드롭스</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="218">
@@ -3241,11 +3241,11 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>알사탕</t>
+          <t>캔디 케인</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="219">
@@ -3254,24 +3254,24 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>태피</t>
+          <t>알사탕</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>마시멜로</t>
+          <t>태피</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>계피사탕</t>
+          <t>마시멜로</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -3293,11 +3293,11 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>누가</t>
+          <t>계피사탕</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="223">
@@ -3306,11 +3306,11 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>롤리팝</t>
+          <t>누가</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="224">
@@ -3319,11 +3319,11 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>알사탕</t>
+          <t>롤리팝</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="225">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>코튼 캔디</t>
+          <t>알사탕</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -3341,11 +3341,11 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>누가</t>
+          <t>코튼 캔디</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>후르츠 캔디</t>
+          <t>누가</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -3371,24 +3371,24 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>젤리빈</t>
+          <t>후르츠 캔디</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>태피</t>
+          <t>젤리빈</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="230">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>팝핑 캔디</t>
+          <t>태피</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>껌</t>
+          <t>팝핑 캔디</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>목캔디</t>
+          <t>껌</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>코튼 캔디</t>
+          <t>목캔디</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -3445,11 +3445,11 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>누룽지 사탕</t>
+          <t>코튼 캔디</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -3462,11 +3462,11 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>계피사탕</t>
+          <t>누룽지 사탕</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236">
@@ -3475,11 +3475,11 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>캐러멜</t>
+          <t>계피사탕</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="237">
@@ -3488,11 +3488,11 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>팝핑 캔디</t>
+          <t>캐러멜</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238">
@@ -3501,11 +3501,11 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>롤리팝</t>
+          <t>팝핑 캔디</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="239">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>비타민 캔디</t>
+          <t>롤리팝</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -3523,11 +3523,11 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>껌</t>
+          <t>비타민 캔디</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -3540,11 +3540,11 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>퍼지</t>
+          <t>껌</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242">
@@ -3553,20 +3553,20 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>롤리팝</t>
+          <t>퍼지</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>비타민 캔디</t>
+          <t>롤리팝</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>마시멜로</t>
+          <t>비타민 캔디</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -3592,20 +3592,20 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>구미</t>
+          <t>마시멜로</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>롤리팝</t>
+          <t>구미</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>구미</t>
+          <t>롤리팝</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -3631,11 +3631,11 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>박하사탕</t>
+          <t>구미</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="249">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>알사탕</t>
+          <t>박하사탕</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -3653,11 +3653,11 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>무설탕 캔디</t>
+          <t>알사탕</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>박하사탕</t>
+          <t>무설탕 캔디</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>코튼 캔디</t>
+          <t>박하사탕</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -3692,11 +3692,11 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>누가</t>
+          <t>코튼 캔디</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>버터스카치</t>
+          <t>누가</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -3722,11 +3722,11 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>비타민 캔디</t>
+          <t>버터스카치</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256">
@@ -3735,20 +3735,20 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>캔디 케인</t>
+          <t>비타민 캔디</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>무설탕 캔디</t>
+          <t>캔디 케인</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>박하사탕</t>
+          <t>무설탕 캔디</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -3774,24 +3774,24 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>태피</t>
+          <t>박하사탕</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>후르츠 캔디</t>
+          <t>태피</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="261">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>계피사탕</t>
+          <t>후르츠 캔디</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>코튼 캔디</t>
+          <t>계피사탕</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>팝핑 캔디</t>
+          <t>코튼 캔디</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>퍼지</t>
+          <t>팝핑 캔디</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -3848,11 +3848,11 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>후르츠 캔디</t>
+          <t>퍼지</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -3865,11 +3865,11 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>누가</t>
+          <t>후르츠 캔디</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="267">
@@ -3878,11 +3878,11 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>누룽지 사탕</t>
+          <t>누가</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="268">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>코튼 캔디</t>
+          <t>누룽지 사탕</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -3900,11 +3900,11 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>젤리빈</t>
+          <t>코튼 캔디</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>퍼지</t>
+          <t>젤리빈</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>박하사탕</t>
+          <t>퍼지</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>드롭스</t>
+          <t>박하사탕</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>무설탕 캔디</t>
+          <t>드롭스</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -3965,11 +3965,11 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>박하사탕</t>
+          <t>무설탕 캔디</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>목캔디</t>
+          <t>박하사탕</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>계피사탕</t>
+          <t>목캔디</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -4004,11 +4004,11 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>누룽지 사탕</t>
+          <t>계피사탕</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>토피</t>
+          <t>누룽지 사탕</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>박하사탕</t>
+          <t>토피</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>캔디 케인</t>
+          <t>박하사탕</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -4060,24 +4060,24 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>캐러멜</t>
+          <t>캔디 케인</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>젤리빈</t>
+          <t>캐러멜</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="283">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>목캔디</t>
+          <t>젤리빈</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -4099,11 +4099,11 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>팝핑 캔디</t>
+          <t>목캔디</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="285">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>캐러멜</t>
+          <t>팝핑 캔디</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -4121,15 +4121,15 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>코튼 캔디</t>
+          <t>캐러멜</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="287">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>목캔디</t>
+          <t>코튼 캔디</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -4151,24 +4151,24 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>캐러멜</t>
+          <t>목캔디</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>누룽지 사탕</t>
+          <t>캐러멜</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="290">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>후르츠 캔디</t>
+          <t>누룽지 사탕</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>버터스카치</t>
+          <t>후르츠 캔디</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -4199,11 +4199,11 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>껌</t>
+          <t>버터스카치</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>목캔디</t>
+          <t>껌</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>누룽지 사탕</t>
+          <t>목캔디</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -4238,15 +4238,15 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>캐러멜</t>
+          <t>누룽지 사탕</t>
         </is>
       </c>
       <c r="C295" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="296">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>무설탕 캔디</t>
+          <t>캐러멜</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -4268,11 +4268,11 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>계피사탕</t>
+          <t>무설탕 캔디</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="298">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>팝핑 캔디</t>
+          <t>계피사탕</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -4294,24 +4294,24 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>퍼지</t>
+          <t>팝핑 캔디</t>
         </is>
       </c>
       <c r="C299" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>코튼 캔디</t>
+          <t>퍼지</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="301">
@@ -4320,11 +4320,11 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>락 캔디</t>
+          <t>코튼 캔디</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="302">
@@ -4333,11 +4333,11 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>후르츠 캔디</t>
+          <t>락 캔디</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="303">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>구미</t>
+          <t>후르츠 캔디</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>후르츠 캔디</t>
+          <t>구미</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="305">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>롤리팝</t>
+          <t>후르츠 캔디</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>박하사탕</t>
+          <t>롤리팝</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>락 캔디</t>
+          <t>박하사탕</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>태피</t>
+          <t>락 캔디</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>껌</t>
+          <t>태피</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -4433,11 +4433,11 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>드롭스</t>
+          <t>껌</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>퍼지</t>
+          <t>드롭스</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>누룽지 사탕</t>
+          <t>퍼지</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -4472,11 +4472,11 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>알사탕</t>
+          <t>누룽지 사탕</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>껌</t>
+          <t>알사탕</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -4502,11 +4502,11 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>젤리빈</t>
+          <t>껌</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316">
@@ -4515,11 +4515,11 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>목캔디</t>
+          <t>젤리빈</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="317">
@@ -4528,24 +4528,24 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>팝핑 캔디</t>
+          <t>목캔디</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>목캔디</t>
+          <t>팝핑 캔디</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="319">
@@ -4554,11 +4554,11 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>드롭스</t>
+          <t>목캔디</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="320">
@@ -4567,11 +4567,11 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>버터스카치</t>
+          <t>드롭스</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="321">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>박하사탕</t>
+          <t>버터스카치</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -4593,11 +4593,11 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>누룽지 사탕</t>
+          <t>박하사탕</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="323">
@@ -4606,24 +4606,24 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>껌</t>
+          <t>누룽지 사탕</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>토피</t>
+          <t>껌</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="325">
@@ -4632,11 +4632,11 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>비타민 캔디</t>
+          <t>토피</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="326">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>목캔디</t>
+          <t>비타민 캔디</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -4654,11 +4654,11 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>태피</t>
+          <t>목캔디</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>누룽지 사탕</t>
+          <t>태피</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -4684,11 +4684,11 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>롤리팝</t>
+          <t>누룽지 사탕</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
@@ -4697,24 +4697,24 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>캐러멜</t>
+          <t>롤리팝</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>롤리팝</t>
+          <t>캐러멜</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>토피</t>
+          <t>롤리팝</t>
         </is>
       </c>
       <c r="C332" t="n">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>계피사탕</t>
+          <t>토피</t>
         </is>
       </c>
       <c r="C333" t="n">
@@ -4749,11 +4749,11 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>코튼 캔디</t>
+          <t>계피사탕</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="335">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>캔디 케인</t>
+          <t>코튼 캔디</t>
         </is>
       </c>
       <c r="C335" t="n">
@@ -4771,11 +4771,11 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>토피</t>
+          <t>캔디 케인</t>
         </is>
       </c>
       <c r="C336" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>목캔디</t>
+          <t>토피</t>
         </is>
       </c>
       <c r="C337" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>태피</t>
+          <t>목캔디</t>
         </is>
       </c>
       <c r="C338" t="n">
@@ -4810,11 +4810,11 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>캔디 케인</t>
+          <t>태피</t>
         </is>
       </c>
       <c r="C339" t="n">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>알사탕</t>
+          <t>캔디 케인</t>
         </is>
       </c>
       <c r="C340" t="n">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>태피</t>
+          <t>알사탕</t>
         </is>
       </c>
       <c r="C341" t="n">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>드롭스</t>
+          <t>태피</t>
         </is>
       </c>
       <c r="C342" t="n">
@@ -4862,11 +4862,11 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>껌</t>
+          <t>드롭스</t>
         </is>
       </c>
       <c r="C343" t="n">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>퍼지</t>
+          <t>껌</t>
         </is>
       </c>
       <c r="C344" t="n">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>태피</t>
+          <t>퍼지</t>
         </is>
       </c>
       <c r="C345" t="n">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>코튼 캔디</t>
+          <t>태피</t>
         </is>
       </c>
       <c r="C346" t="n">
@@ -4914,11 +4914,11 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>후르츠 캔디</t>
+          <t>코튼 캔디</t>
         </is>
       </c>
       <c r="C347" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>알사탕</t>
+          <t>후르츠 캔디</t>
         </is>
       </c>
       <c r="C348" t="n">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>팝핑 캔디</t>
+          <t>알사탕</t>
         </is>
       </c>
       <c r="C349" t="n">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>버터스카치</t>
+          <t>팝핑 캔디</t>
         </is>
       </c>
       <c r="C350" t="n">
@@ -4966,11 +4966,11 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>롤리팝</t>
+          <t>버터스카치</t>
         </is>
       </c>
       <c r="C351" t="n">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>마시멜로</t>
+          <t>롤리팝</t>
         </is>
       </c>
       <c r="C352" t="n">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>캔디 케인</t>
+          <t>마시멜로</t>
         </is>
       </c>
       <c r="C353" t="n">
@@ -5009,11 +5009,11 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>계피사탕</t>
+          <t>캔디 케인</t>
         </is>
       </c>
       <c r="C354" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="355">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>젤리빈</t>
+          <t>계피사탕</t>
         </is>
       </c>
       <c r="C355" t="n">
@@ -5035,20 +5035,20 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>토피</t>
+          <t>젤리빈</t>
         </is>
       </c>
       <c r="C356" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>캔디 케인</t>
+          <t>토피</t>
         </is>
       </c>
       <c r="C357" t="n">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>드롭스</t>
+          <t>캔디 케인</t>
         </is>
       </c>
       <c r="C358" t="n">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>코튼 캔디</t>
+          <t>드롭스</t>
         </is>
       </c>
       <c r="C359" t="n">
@@ -5087,11 +5087,11 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>계피사탕</t>
+          <t>코튼 캔디</t>
         </is>
       </c>
       <c r="C360" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="361">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>누가</t>
+          <t>계피사탕</t>
         </is>
       </c>
       <c r="C361" t="n">
@@ -5109,15 +5109,15 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>후르츠 캔디</t>
+          <t>누가</t>
         </is>
       </c>
       <c r="C362" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="363">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>박하사탕</t>
+          <t>후르츠 캔디</t>
         </is>
       </c>
       <c r="C363" t="n">
@@ -5139,11 +5139,11 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>토피</t>
+          <t>박하사탕</t>
         </is>
       </c>
       <c r="C364" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="365">
@@ -5152,11 +5152,11 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>락 캔디</t>
+          <t>토피</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="366">
@@ -5165,24 +5165,24 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>구미</t>
+          <t>락 캔디</t>
         </is>
       </c>
       <c r="C366" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>코튼 캔디</t>
+          <t>구미</t>
         </is>
       </c>
       <c r="C367" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="368">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>목캔디</t>
+          <t>코튼 캔디</t>
         </is>
       </c>
       <c r="C368" t="n">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>퍼지</t>
+          <t>목캔디</t>
         </is>
       </c>
       <c r="C369" t="n">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>드롭스</t>
+          <t>퍼지</t>
         </is>
       </c>
       <c r="C370" t="n">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>버터스카치</t>
+          <t>드롭스</t>
         </is>
       </c>
       <c r="C371" t="n">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>후르츠 캔디</t>
+          <t>버터스카치</t>
         </is>
       </c>
       <c r="C372" t="n">
@@ -5252,15 +5252,15 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>비타민 캔디</t>
+          <t>후르츠 캔디</t>
         </is>
       </c>
       <c r="C373" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="374">
@@ -5269,11 +5269,11 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>후르츠 캔디</t>
+          <t>비타민 캔디</t>
         </is>
       </c>
       <c r="C374" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="375">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>롤리팝</t>
+          <t>후르츠 캔디</t>
         </is>
       </c>
       <c r="C375" t="n">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>버터스카치</t>
+          <t>롤리팝</t>
         </is>
       </c>
       <c r="C376" t="n">
@@ -5304,15 +5304,15 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>토피</t>
+          <t>버터스카치</t>
         </is>
       </c>
       <c r="C377" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="378">
@@ -5321,11 +5321,11 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>퍼지</t>
+          <t>토피</t>
         </is>
       </c>
       <c r="C378" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="379">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>태피</t>
+          <t>퍼지</t>
         </is>
       </c>
       <c r="C379" t="n">
@@ -5347,11 +5347,11 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>무설탕 캔디</t>
+          <t>태피</t>
         </is>
       </c>
       <c r="C380" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="381">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>구미</t>
+          <t>무설탕 캔디</t>
         </is>
       </c>
       <c r="C381" t="n">
@@ -5373,24 +5373,24 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>버터스카치</t>
+          <t>구미</t>
         </is>
       </c>
       <c r="C382" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>비타민 캔디</t>
+          <t>버터스카치</t>
         </is>
       </c>
       <c r="C383" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="384">
@@ -5399,11 +5399,11 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>계피사탕</t>
+          <t>비타민 캔디</t>
         </is>
       </c>
       <c r="C384" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="385">
@@ -5412,7 +5412,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>후르츠 캔디</t>
+          <t>계피사탕</t>
         </is>
       </c>
       <c r="C385" t="n">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>롤리팝</t>
+          <t>후르츠 캔디</t>
         </is>
       </c>
       <c r="C386" t="n">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>태피</t>
+          <t>롤리팝</t>
         </is>
       </c>
       <c r="C387" t="n">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>드롭스</t>
+          <t>태피</t>
         </is>
       </c>
       <c r="C388" t="n">
@@ -5460,15 +5460,15 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>토피</t>
+          <t>드롭스</t>
         </is>
       </c>
       <c r="C389" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="390">
@@ -5477,11 +5477,11 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>태피</t>
+          <t>토피</t>
         </is>
       </c>
       <c r="C390" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="391">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>박하사탕</t>
+          <t>태피</t>
         </is>
       </c>
       <c r="C391" t="n">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>코튼 캔디</t>
+          <t>박하사탕</t>
         </is>
       </c>
       <c r="C392" t="n">
@@ -5512,11 +5512,11 @@
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>무설탕 캔디</t>
+          <t>코튼 캔디</t>
         </is>
       </c>
       <c r="C393" t="n">
@@ -5529,11 +5529,11 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>퍼지</t>
+          <t>무설탕 캔디</t>
         </is>
       </c>
       <c r="C394" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="395">
@@ -5542,11 +5542,11 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>코튼 캔디</t>
+          <t>퍼지</t>
         </is>
       </c>
       <c r="C395" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="396">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>버터스카치</t>
+          <t>코튼 캔디</t>
         </is>
       </c>
       <c r="C396" t="n">
@@ -5568,24 +5568,24 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>껌</t>
+          <t>버터스카치</t>
         </is>
       </c>
       <c r="C397" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>구미</t>
+          <t>껌</t>
         </is>
       </c>
       <c r="C398" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="399">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>캐러멜</t>
+          <t>구미</t>
         </is>
       </c>
       <c r="C399" t="n">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>코튼 캔디</t>
+          <t>캐러멜</t>
         </is>
       </c>
       <c r="C400" t="n">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>태피</t>
+          <t>코튼 캔디</t>
         </is>
       </c>
       <c r="C401" t="n">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>퍼지</t>
+          <t>태피</t>
         </is>
       </c>
       <c r="C402" t="n">
@@ -5642,11 +5642,11 @@
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>팝핑 캔디</t>
+          <t>퍼지</t>
         </is>
       </c>
       <c r="C403" t="n">
@@ -5659,11 +5659,11 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>캐러멜</t>
+          <t>팝핑 캔디</t>
         </is>
       </c>
       <c r="C404" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="405">
@@ -5672,11 +5672,11 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>목캔디</t>
+          <t>캐러멜</t>
         </is>
       </c>
       <c r="C405" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="406">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>누룽지 사탕</t>
+          <t>목캔디</t>
         </is>
       </c>
       <c r="C406" t="n">
@@ -5698,11 +5698,11 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>계피사탕</t>
+          <t>누룽지 사탕</t>
         </is>
       </c>
       <c r="C407" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="408">
@@ -5711,20 +5711,20 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>태피</t>
+          <t>계피사탕</t>
         </is>
       </c>
       <c r="C408" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>코튼 캔디</t>
+          <t>태피</t>
         </is>
       </c>
       <c r="C409" t="n">
@@ -5737,11 +5737,11 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>알사탕</t>
+          <t>코튼 캔디</t>
         </is>
       </c>
       <c r="C410" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="411">
@@ -5750,11 +5750,11 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>무설탕 캔디</t>
+          <t>알사탕</t>
         </is>
       </c>
       <c r="C411" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="412">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>비타민 캔디</t>
+          <t>무설탕 캔디</t>
         </is>
       </c>
       <c r="C412" t="n">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>캐러멜</t>
+          <t>비타민 캔디</t>
         </is>
       </c>
       <c r="C413" t="n">
@@ -5789,20 +5789,20 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>누가</t>
+          <t>캐러멜</t>
         </is>
       </c>
       <c r="C414" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>캐러멜</t>
+          <t>누가</t>
         </is>
       </c>
       <c r="C415" t="n">
@@ -5815,11 +5815,11 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>계피사탕</t>
+          <t>캐러멜</t>
         </is>
       </c>
       <c r="C416" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="417">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>태피</t>
+          <t>계피사탕</t>
         </is>
       </c>
       <c r="C417" t="n">
@@ -5837,15 +5837,15 @@
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>젤리빈</t>
+          <t>태피</t>
         </is>
       </c>
       <c r="C418" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="419">
@@ -5854,11 +5854,11 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>코튼 캔디</t>
+          <t>젤리빈</t>
         </is>
       </c>
       <c r="C419" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="420">
@@ -5867,11 +5867,11 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>계피사탕</t>
+          <t>코튼 캔디</t>
         </is>
       </c>
       <c r="C420" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="421">
@@ -5880,11 +5880,11 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>구미</t>
+          <t>계피사탕</t>
         </is>
       </c>
       <c r="C421" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="422">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>마시멜로</t>
+          <t>구미</t>
         </is>
       </c>
       <c r="C422" t="n">
@@ -5902,11 +5902,11 @@
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>코튼 캔디</t>
+          <t>마시멜로</t>
         </is>
       </c>
       <c r="C423" t="n">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>박하사탕</t>
+          <t>코튼 캔디</t>
         </is>
       </c>
       <c r="C424" t="n">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>캐러멜</t>
+          <t>박하사탕</t>
         </is>
       </c>
       <c r="C425" t="n">
@@ -5945,24 +5945,24 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>구미</t>
+          <t>캐러멜</t>
         </is>
       </c>
       <c r="C426" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>박하사탕</t>
+          <t>구미</t>
         </is>
       </c>
       <c r="C427" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="428">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>캔디 케인</t>
+          <t>박하사탕</t>
         </is>
       </c>
       <c r="C428" t="n">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>코튼 캔디</t>
+          <t>캔디 케인</t>
         </is>
       </c>
       <c r="C429" t="n">
@@ -5997,11 +5997,11 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>캐러멜</t>
+          <t>코튼 캔디</t>
         </is>
       </c>
       <c r="C430" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="431">
@@ -6010,20 +6010,20 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>계피사탕</t>
+          <t>캐러멜</t>
         </is>
       </c>
       <c r="C431" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>드롭스</t>
+          <t>계피사탕</t>
         </is>
       </c>
       <c r="C432" t="n">
@@ -6036,11 +6036,11 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>롤리팝</t>
+          <t>드롭스</t>
         </is>
       </c>
       <c r="C433" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="434">
@@ -6049,11 +6049,11 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>캔디 케인</t>
+          <t>롤리팝</t>
         </is>
       </c>
       <c r="C434" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="435">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>마시멜로</t>
+          <t>캔디 케인</t>
         </is>
       </c>
       <c r="C435" t="n">
@@ -6071,11 +6071,11 @@
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>젤리빈</t>
+          <t>마시멜로</t>
         </is>
       </c>
       <c r="C436" t="n">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>태피</t>
+          <t>젤리빈</t>
         </is>
       </c>
       <c r="C437" t="n">
@@ -6101,10 +6101,23 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
+          <t>태피</t>
+        </is>
+      </c>
+      <c r="C438" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="n">
+        <v>100</v>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
           <t>락 캔디</t>
         </is>
       </c>
-      <c r="C438" t="n">
+      <c r="C439" t="n">
         <v>2</v>
       </c>
     </row>
